--- a/data/trans_orig/IP16_n_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R-Provincia-trans_orig.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17512</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>36991</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>61837</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>82124</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>106924</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>177034</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -8131,12 +8131,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39951</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8803,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -9475,12 +9475,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -10036,12 +10036,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10071,12 +10071,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10232,12 +10232,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -10708,12 +10708,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10723,12 +10723,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10778,12 +10778,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -11491,12 +11491,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11506,12 +11506,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>40532</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11576,12 +11576,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -12052,12 +12052,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12067,12 +12067,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12087,12 +12087,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12122,12 +12122,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12137,12 +12137,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -12163,12 +12163,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>20653</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>30298</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>39334</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -12542,7 +12542,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -12613,12 +12613,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12628,12 +12628,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12698,12 +12698,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -12724,12 +12724,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -13667,12 +13667,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13702,12 +13702,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -13778,12 +13778,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>12863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -14304,12 +14304,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -14415,12 +14415,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14465,12 +14465,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -15648,12 +15648,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15663,12 +15663,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15683,12 +15683,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15698,12 +15698,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15718,12 +15718,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15733,12 +15733,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -15759,12 +15759,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15794,12 +15794,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15829,12 +15829,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16390,12 +16390,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16405,12 +16405,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -16501,12 +16501,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16516,12 +16516,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -17664,12 +17664,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17679,12 +17679,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17734,12 +17734,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17749,12 +17749,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -17775,12 +17775,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -17790,12 +17790,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -17845,12 +17845,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18406,12 +18406,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18421,12 +18421,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18462,12 +18462,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18482,12 +18482,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18497,12 +18497,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18517,12 +18517,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>38521</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>44291</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18532,12 +18532,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -18967,12 +18967,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -18987,7 +18987,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -19008,12 +19008,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19023,12 +19023,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19058,12 +19058,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19093,12 +19093,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -19119,12 +19119,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19154,12 +19154,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19169,12 +19169,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19189,12 +19189,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19204,12 +19204,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -19845,7 +19845,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -19916,12 +19916,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -19931,12 +19931,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -19956,7 +19956,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -19986,12 +19986,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -20001,12 +20001,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -20027,12 +20027,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29764</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -20042,12 +20042,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -20062,12 +20062,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -20077,12 +20077,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -20097,12 +20097,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42858</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50785</t>
+          <t>50418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -20112,12 +20112,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -20371,7 +20371,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -20497,7 +20497,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -20547,12 +20547,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -20562,12 +20562,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -20588,12 +20588,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -20603,12 +20603,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -20658,12 +20658,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36786</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -20673,12 +20673,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -20699,12 +20699,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>58604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -20714,12 +20714,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -20734,12 +20734,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25490</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -20769,12 +20769,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>66014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98163</t>
+          <t>97511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -20784,12 +20784,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -21260,12 +21260,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -21295,12 +21295,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -21310,12 +21310,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -21330,12 +21330,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -21345,12 +21345,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -21386,12 +21386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -21406,12 +21406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -21421,12 +21421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -21456,12 +21456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -21861,7 +21861,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -21932,12 +21932,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -21947,12 +21947,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -21967,12 +21967,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>492</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -21982,12 +21982,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -22002,12 +22002,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -22017,12 +22017,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -22043,12 +22043,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -22058,12 +22058,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -22078,12 +22078,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -22093,12 +22093,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -22113,12 +22113,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -22498,7 +22498,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -22563,12 +22563,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -22578,12 +22578,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -22604,12 +22604,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -22619,12 +22619,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>287</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -22654,12 +22654,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -22674,12 +22674,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -22689,12 +22689,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -22715,12 +22715,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -22730,12 +22730,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -22750,12 +22750,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -22765,12 +22765,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -22785,12 +22785,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -23311,12 +23311,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -23346,12 +23346,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -23361,12 +23361,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -23422,12 +23422,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -23437,12 +23437,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -23457,12 +23457,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -23472,12 +23472,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23620,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -23635,7 +23635,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -23731,7 +23731,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -23796,12 +23796,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -23811,12 +23811,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -23837,12 +23837,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -23852,12 +23852,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -23872,12 +23872,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>877</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -23907,12 +23907,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -23922,12 +23922,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -23948,12 +23948,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -23983,12 +23983,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -23998,12 +23998,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -24018,12 +24018,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -24033,12 +24033,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -24059,12 +24059,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -24074,12 +24074,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -24094,12 +24094,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>34117</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -24109,12 +24109,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -24129,12 +24129,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>33990</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -24529,7 +24529,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -24549,7 +24549,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -24620,12 +24620,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -24635,12 +24635,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -24655,12 +24655,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -24670,12 +24670,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -24690,12 +24690,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -24705,12 +24705,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -24746,12 +24746,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -24781,12 +24781,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -24801,12 +24801,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -24816,12 +24816,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -25034,7 +25034,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -25070,12 +25070,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -25090,7 +25090,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -25140,12 +25140,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -25155,12 +25155,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -25196,7 +25196,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -25231,12 +25231,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -25251,12 +25251,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -25292,12 +25292,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>53074</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -25307,12 +25307,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -25327,12 +25327,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40349</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -25342,12 +25342,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -25362,12 +25362,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>106002</t>
+          <t>107821</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -25377,12 +25377,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -25403,12 +25403,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -25418,12 +25418,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -25438,12 +25438,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -25473,12 +25473,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -25488,12 +25488,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
